--- a/Plotting/Latex/filtered_data_Zeeland.xlsx
+++ b/Plotting/Latex/filtered_data_Zeeland.xlsx
@@ -907,7 +907,7 @@
         <v>951</v>
       </c>
       <c r="G13" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I14" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="15">
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G15" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I16" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="17">
@@ -1191,7 +1191,7 @@
         <v>689</v>
       </c>
       <c r="E21" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F21" t="n">
         <v>440</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E26" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F26" t="n">
         <v>299</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F30" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>146</v>
       </c>
       <c r="I30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31">
@@ -1653,7 +1653,7 @@
         <v>43</v>
       </c>
       <c r="I33" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I35" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36">
@@ -1748,19 +1748,19 @@
         <v>379</v>
       </c>
       <c r="E36" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F36" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G36" t="n">
         <v>383</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37">
@@ -1801,7 +1801,7 @@
         <v>383</v>
       </c>
       <c r="I37" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="38">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16565</v>
+        <v>16566</v>
       </c>
       <c r="E38" t="n">
         <v>2325</v>
@@ -1831,7 +1831,7 @@
         <v>5113</v>
       </c>
       <c r="H38" t="n">
-        <v>10714</v>
+        <v>10715</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="E40" t="n">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>182</v>
       </c>
       <c r="H42" t="n">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5724</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="48">
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>10251</v>
+        <v>10252</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
